--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2344-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2344-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43E89099-482B-4C66-85FF-9104D547235E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D39107D-AFB8-48A9-BCB4-B0B275864FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DD0EC1A6-7DEC-4A35-AB8C-7B344F2652C3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2122A3B7-8233-4683-A4CB-473BDDE0FF52}"/>
   </bookViews>
   <sheets>
     <sheet name="2344-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,22 +1490,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FC3D5E-B310-4CAC-AD81-E280A7672D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED48E5D5-E037-48A9-A96C-479C60650636}">
   <dimension ref="A1:R60"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1659,7 +1659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2025</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38">
         <v>2024</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2023</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2022</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2021</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2020</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2019</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2018</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2017</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2016</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2015</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2014</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2013</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2012</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2011</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2010</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2009</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2008</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2007</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2006</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>2005</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2004</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>2003</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>2002</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>2001</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>2000</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>1999</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>1998</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>1997</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38">
         <v>1996</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>1995</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="38">
         <v>1994</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="40">
         <v>1993</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="38">
         <v>1992</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="40" t="s">
         <v>48</v>
       </c>
